--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Desktop\Ny mappe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F16EB6-A037-44F9-8AE6-81CF83BCB569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF69D64-E3C5-4FD7-9839-17D30FF9489A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="36">
   <si>
     <t>Ejer</t>
   </si>
@@ -117,6 +117,33 @@
   </si>
   <si>
     <t>Koordinater</t>
+  </si>
+  <si>
+    <t>Anettevej 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jens Kr. Kristiansen </t>
+  </si>
+  <si>
+    <t>Der er en anden adresse med engdalsvej 107</t>
+  </si>
+  <si>
+    <t>Ib Hedegård Kristensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F.M Poulsens </t>
+  </si>
+  <si>
+    <t>F.M Poulsens Gartneri</t>
+  </si>
+  <si>
+    <t>Engdalsvej 102</t>
+  </si>
+  <si>
+    <t>21b, 10c, 13l, 7h, 8æ,</t>
+  </si>
+  <si>
+    <t>1256 m2</t>
   </si>
 </sst>
 </file>
@@ -515,19 +542,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9410E6E1-B6FD-499D-B70E-01FA93ABCF11}">
   <dimension ref="A1:K103"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="5" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" customWidth="1"/>
-    <col min="9" max="9" width="24.140625" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" customWidth="1"/>
+    <col min="1" max="2" width="14.81640625" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" customWidth="1"/>
+    <col min="4" max="4" width="22.90625" customWidth="1"/>
+    <col min="5" max="6" width="17.26953125" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" customWidth="1"/>
+    <col min="8" max="8" width="25.1796875" customWidth="1"/>
+    <col min="9" max="9" width="24.1796875" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" customWidth="1"/>
+    <col min="11" max="11" width="36.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -562,7 +590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -589,7 +617,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -606,7 +634,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -625,7 +653,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -648,40 +676,63 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>1937</v>
+      </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K6" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>1902</v>
+      </c>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K7" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -698,7 +749,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -715,7 +766,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -732,7 +783,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -749,7 +800,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -766,7 +817,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -783,7 +834,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -800,7 +851,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -817,7 +868,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -834,7 +885,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -851,7 +902,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -868,7 +919,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -885,7 +936,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -902,7 +953,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -919,7 +970,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -936,7 +987,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -953,7 +1004,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -970,7 +1021,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -987,7 +1038,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1004,7 +1055,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1021,7 +1072,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1038,7 +1089,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1055,7 +1106,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1072,7 +1123,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1089,7 +1140,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1106,7 +1157,7 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1123,7 +1174,7 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1140,7 +1191,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1157,7 +1208,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1174,7 +1225,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1191,7 +1242,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1208,7 +1259,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1225,7 +1276,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1242,7 +1293,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1259,7 +1310,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1276,7 +1327,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1293,7 +1344,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1310,7 +1361,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1327,7 +1378,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1344,7 +1395,7 @@
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1361,7 +1412,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1378,7 +1429,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1395,7 +1446,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1412,7 +1463,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1429,7 +1480,7 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1446,7 +1497,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1463,7 +1514,7 @@
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1480,7 +1531,7 @@
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1497,7 +1548,7 @@
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1514,7 +1565,7 @@
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1531,7 +1582,7 @@
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1548,7 +1599,7 @@
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1565,7 +1616,7 @@
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1582,7 +1633,7 @@
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1599,7 +1650,7 @@
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1616,7 +1667,7 @@
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1633,7 +1684,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1650,7 +1701,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1667,7 +1718,7 @@
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1684,7 +1735,7 @@
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1701,7 +1752,7 @@
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1718,7 +1769,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1735,7 +1786,7 @@
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1750,7 +1801,7 @@
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1767,7 +1818,7 @@
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1784,7 +1835,7 @@
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1801,7 +1852,7 @@
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1818,7 +1869,7 @@
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1835,7 +1886,7 @@
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1852,7 +1903,7 @@
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1869,7 +1920,7 @@
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1886,7 +1937,7 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1903,7 +1954,7 @@
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1920,7 +1971,7 @@
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1937,7 +1988,7 @@
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1954,7 +2005,7 @@
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1969,7 +2020,7 @@
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1986,7 +2037,7 @@
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -2003,7 +2054,7 @@
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -2018,7 +2069,7 @@
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -2035,7 +2086,7 @@
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -2052,7 +2103,7 @@
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -2069,7 +2120,7 @@
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -2086,7 +2137,7 @@
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -2103,7 +2154,7 @@
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -2120,7 +2171,7 @@
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -2137,7 +2188,7 @@
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -2154,7 +2205,7 @@
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -2171,7 +2222,7 @@
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2188,7 +2239,7 @@
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2205,7 +2256,7 @@
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2222,7 +2273,7 @@
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2239,7 +2290,7 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2256,7 +2307,7 @@
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2271,7 +2322,7 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2286,7 +2337,7 @@
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF69D64-E3C5-4FD7-9839-17D30FF9489A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4778C20E-EC61-4ACF-BED5-23F677F8916B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="48">
   <si>
     <t>Ejer</t>
   </si>
@@ -144,6 +144,42 @@
   </si>
   <si>
     <t>1256 m2</t>
+  </si>
+  <si>
+    <t>Hansen</t>
+  </si>
+  <si>
+    <t>ca. 1960</t>
+  </si>
+  <si>
+    <t>Engdalsvej</t>
+  </si>
+  <si>
+    <t>16ap - 9c - 9m</t>
+  </si>
+  <si>
+    <t>Hansens Frilandsgartner</t>
+  </si>
+  <si>
+    <t>Enghavevej 58</t>
+  </si>
+  <si>
+    <t>J.K. Touborg</t>
+  </si>
+  <si>
+    <t>J.K. Touborgs Handelsgartneri</t>
+  </si>
+  <si>
+    <t>5700 m2</t>
+  </si>
+  <si>
+    <t>Petersminde</t>
+  </si>
+  <si>
+    <t>C. Kragh Sørensen</t>
+  </si>
+  <si>
+    <t>8a, 9a, 7a, 8b.</t>
   </si>
 </sst>
 </file>
@@ -173,7 +209,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -196,17 +232,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,7 +600,7 @@
     <col min="5" max="6" width="17.26953125" customWidth="1"/>
     <col min="7" max="7" width="21.54296875" customWidth="1"/>
     <col min="8" max="8" width="25.1796875" customWidth="1"/>
-    <col min="9" max="9" width="24.1796875" customWidth="1"/>
+    <col min="9" max="9" width="25.7265625" customWidth="1"/>
     <col min="10" max="10" width="17.81640625" customWidth="1"/>
     <col min="11" max="11" width="36.08984375" customWidth="1"/>
   </cols>
@@ -618,7 +668,7 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
@@ -704,50 +754,50 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1">
+      <c r="F7" s="4"/>
+      <c r="G7" s="4">
         <v>1902</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="4"/>
+      <c r="K7" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -756,13 +806,23 @@
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
@@ -773,15 +833,25 @@
       <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>1933</v>
+      </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
@@ -790,13 +860,21 @@
       <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>1909</v>
+      </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4778C20E-EC61-4ACF-BED5-23F677F8916B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B244F6B-3B1B-4AE6-9861-DAB23610CAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="124">
   <si>
     <t>Ejer</t>
   </si>
@@ -180,6 +180,234 @@
   </si>
   <si>
     <t>8a, 9a, 7a, 8b.</t>
+  </si>
+  <si>
+    <t>5000 m2</t>
+  </si>
+  <si>
+    <t>Jenny Kragh Sørensen</t>
+  </si>
+  <si>
+    <t>8a</t>
+  </si>
+  <si>
+    <t>Ringvejen</t>
+  </si>
+  <si>
+    <t>Gellerup/Åbyhøj</t>
+  </si>
+  <si>
+    <t>Gartneriet Petersminde</t>
+  </si>
+  <si>
+    <t>40y, 36, 7b/76?</t>
+  </si>
+  <si>
+    <t>Jens Kristian Kristiansen</t>
+  </si>
+  <si>
+    <t>Nøjsomhedsvej</t>
+  </si>
+  <si>
+    <t>Engdalsvej 110</t>
+  </si>
+  <si>
+    <t>Zenia</t>
+  </si>
+  <si>
+    <t>15bc,5ba. mf.</t>
+  </si>
+  <si>
+    <t>Svend Aage Nielsen</t>
+  </si>
+  <si>
+    <t>Engdalsvej 112</t>
+  </si>
+  <si>
+    <t>Ronald Jensen</t>
+  </si>
+  <si>
+    <t>1bg</t>
+  </si>
+  <si>
+    <t>15bc</t>
+  </si>
+  <si>
+    <t>Svendsen</t>
+  </si>
+  <si>
+    <t>40ak, 45am, 40al,40m</t>
+  </si>
+  <si>
+    <t>Stiene Nielsen</t>
+  </si>
+  <si>
+    <t>Max Nielsen og Ragnar Nielsen</t>
+  </si>
+  <si>
+    <t>45am, 40al</t>
+  </si>
+  <si>
+    <t>40ac, 11ag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gunner Rasmussen </t>
+  </si>
+  <si>
+    <t>Kristian Georg Svendsen</t>
+  </si>
+  <si>
+    <t>21g, 3f, mf.</t>
+  </si>
+  <si>
+    <t>Flora</t>
+  </si>
+  <si>
+    <t>A.M Mortensen</t>
+  </si>
+  <si>
+    <t>16bg-16ad</t>
+  </si>
+  <si>
+    <t>Frank Mortensen</t>
+  </si>
+  <si>
+    <t>Enghavevej</t>
+  </si>
+  <si>
+    <t>16bg-16ce</t>
+  </si>
+  <si>
+    <t>Carl Nielsen</t>
+  </si>
+  <si>
+    <t>Carl Nielsens Gartneri</t>
+  </si>
+  <si>
+    <t>16bc-16bk mf.</t>
+  </si>
+  <si>
+    <t>8236 m2</t>
+  </si>
+  <si>
+    <t>Johanne Corfitsen</t>
+  </si>
+  <si>
+    <t>Johanne Corfitsens Gartneri</t>
+  </si>
+  <si>
+    <t>Hovedgaden 15</t>
+  </si>
+  <si>
+    <t>9173 m2</t>
+  </si>
+  <si>
+    <t>11ø, 13i</t>
+  </si>
+  <si>
+    <t>Jørgen Leonard  Abel</t>
+  </si>
+  <si>
+    <t>15v - 15ap m.fl.</t>
+  </si>
+  <si>
+    <t>Hovedgaden 114</t>
+  </si>
+  <si>
+    <t>Jens Heindorf</t>
+  </si>
+  <si>
+    <t>9514 m2</t>
+  </si>
+  <si>
+    <t>5bæ, 5 ab. 5aa. M.fl</t>
+  </si>
+  <si>
+    <t>Poul Heindorf</t>
+  </si>
+  <si>
+    <t>Silkeborgvej 670</t>
+  </si>
+  <si>
+    <t>2800 m2</t>
+  </si>
+  <si>
+    <t>Ejner Larsen</t>
+  </si>
+  <si>
+    <t>6u -5cc -</t>
+  </si>
+  <si>
+    <t>Ejner Larsens Garneri - Høiriis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folmer Jørgensen </t>
+  </si>
+  <si>
+    <t>10aø</t>
+  </si>
+  <si>
+    <t>Christian P. Kjær</t>
+  </si>
+  <si>
+    <t>16bn - 16bf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axel Hansen </t>
+  </si>
+  <si>
+    <t>Villa Canto</t>
+  </si>
+  <si>
+    <t>Hovedgaden 99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4by - 4 dn- 3be </t>
+  </si>
+  <si>
+    <t>6572 m2</t>
+  </si>
+  <si>
+    <t>4by - 4 dn</t>
+  </si>
+  <si>
+    <t>Christian Kristiansen</t>
+  </si>
+  <si>
+    <t>Silkeborgvej</t>
+  </si>
+  <si>
+    <t>A. Christiansens Handelsgartneri</t>
+  </si>
+  <si>
+    <t>Albert Christiansen</t>
+  </si>
+  <si>
+    <t>Brabrand 11</t>
+  </si>
+  <si>
+    <t>11i - 14d - 15c- 11g - 3k-  4g.</t>
+  </si>
+  <si>
+    <t>Tom</t>
+  </si>
+  <si>
+    <t>Langdalsgaard</t>
+  </si>
+  <si>
+    <t>Hartvig de Linde</t>
+  </si>
+  <si>
+    <t>4d - 18l - 22b- 25b - 28b - 29b - 29k</t>
+  </si>
+  <si>
+    <t>7913 m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Gjørtz Christiansen </t>
+  </si>
+  <si>
+    <t>1m</t>
   </si>
 </sst>
 </file>
@@ -195,7 +423,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,6 +433,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -249,7 +483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -257,6 +491,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,10 +842,10 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="14.81640625" customWidth="1"/>
-    <col min="3" max="3" width="20.26953125" customWidth="1"/>
-    <col min="4" max="4" width="22.90625" customWidth="1"/>
+    <col min="3" max="3" width="26.54296875" customWidth="1"/>
+    <col min="4" max="4" width="28.1796875" customWidth="1"/>
     <col min="5" max="6" width="17.26953125" customWidth="1"/>
-    <col min="7" max="7" width="21.54296875" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" style="9" customWidth="1"/>
     <col min="8" max="8" width="25.1796875" customWidth="1"/>
     <col min="9" max="9" width="25.7265625" customWidth="1"/>
     <col min="10" max="10" width="17.81640625" customWidth="1"/>
@@ -624,7 +871,7 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -657,7 +904,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="1"/>
@@ -672,7 +919,9 @@
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -697,7 +946,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -720,7 +969,7 @@
         <v>25</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="6"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -741,7 +990,7 @@
         <v>27</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1">
+      <c r="G6" s="6">
         <v>1937</v>
       </c>
       <c r="H6" s="1"/>
@@ -770,7 +1019,7 @@
         <v>33</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="G7" s="4">
+      <c r="G7" s="7">
         <v>1902</v>
       </c>
       <c r="H7" s="4"/>
@@ -789,11 +1038,13 @@
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="G8" s="3"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -816,7 +1067,7 @@
         <v>38</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="6" t="s">
         <v>37</v>
       </c>
       <c r="H9" s="1"/>
@@ -841,7 +1092,7 @@
         <v>41</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="1">
+      <c r="G10" s="6">
         <v>1933</v>
       </c>
       <c r="H10" s="1"/>
@@ -854,61 +1105,81 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1">
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="8">
         <v>1909</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="C12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="8">
+        <v>1909</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="B13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
@@ -919,13 +1190,21 @@
       <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="6"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
@@ -936,11 +1215,17 @@
       <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="6"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -953,11 +1238,17 @@
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="6"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -970,32 +1261,44 @@
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="6"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
+      <c r="B18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
@@ -1004,11 +1307,17 @@
       <c r="B19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="C19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="6"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1021,11 +1330,17 @@
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1038,11 +1353,17 @@
       <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="6"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1055,13 +1376,21 @@
       <c r="B22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="6">
+        <v>1921</v>
+      </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
@@ -1072,13 +1401,18 @@
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="C23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="6"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
@@ -1089,15 +1423,25 @@
       <c r="B24" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="C24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
@@ -1106,49 +1450,65 @@
       <c r="B25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="C25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="B27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
@@ -1157,15 +1517,25 @@
       <c r="B28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="C28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="6">
+        <v>1914</v>
+      </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
@@ -1174,15 +1544,21 @@
       <c r="B29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="1"/>
+      <c r="C29" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="6"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
@@ -1191,13 +1567,21 @@
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="C30" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="6">
+        <v>1936</v>
+      </c>
       <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
@@ -1208,11 +1592,19 @@
       <c r="B31" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="C31" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="6">
+        <v>1957</v>
+      </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -1225,11 +1617,17 @@
       <c r="B32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="C32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -1242,15 +1640,25 @@
       <c r="B33" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="C33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
@@ -1259,11 +1667,17 @@
       <c r="B34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="C34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+      <c r="G34" s="6"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -1276,32 +1690,44 @@
       <c r="B35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="C35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
+      <c r="G35" s="6">
+        <v>1870</v>
+      </c>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="I35" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="B36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
@@ -1310,15 +1736,23 @@
       <c r="B37" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
+      <c r="C37" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="I37" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
@@ -1327,11 +1761,17 @@
       <c r="B38" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
+      <c r="C38" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
+      <c r="G38" s="6">
+        <v>1942</v>
+      </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -1348,7 +1788,7 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="G39" s="6"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -1365,7 +1805,7 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
+      <c r="G40" s="6"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -1382,7 +1822,7 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
+      <c r="G41" s="6"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -1399,7 +1839,7 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+      <c r="G42" s="6"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -1416,7 +1856,7 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+      <c r="G43" s="6"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -1433,7 +1873,7 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
+      <c r="G44" s="6"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -1450,7 +1890,7 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
+      <c r="G45" s="6"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -1467,7 +1907,7 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
+      <c r="G46" s="6"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -1484,7 +1924,7 @@
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
+      <c r="G47" s="6"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -1501,7 +1941,7 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
+      <c r="G48" s="6"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -1518,7 +1958,7 @@
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
+      <c r="G49" s="6"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -1535,7 +1975,7 @@
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
+      <c r="G50" s="6"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -1552,7 +1992,7 @@
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
+      <c r="G51" s="6"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -1569,7 +2009,7 @@
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
+      <c r="G52" s="6"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -1586,7 +2026,7 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
+      <c r="G53" s="6"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -1603,7 +2043,7 @@
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="G54" s="6"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -1620,7 +2060,7 @@
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
+      <c r="G55" s="6"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -1637,7 +2077,7 @@
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
+      <c r="G56" s="6"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -1654,7 +2094,7 @@
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
+      <c r="G57" s="6"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -1671,7 +2111,7 @@
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
+      <c r="G58" s="6"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -1688,7 +2128,7 @@
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
+      <c r="G59" s="6"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -1705,7 +2145,7 @@
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
+      <c r="G60" s="6"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -1722,7 +2162,7 @@
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
+      <c r="G61" s="6"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -1739,7 +2179,7 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
+      <c r="G62" s="6"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -1756,7 +2196,7 @@
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
+      <c r="G63" s="6"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -1773,7 +2213,7 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
+      <c r="G64" s="6"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -1790,7 +2230,7 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
+      <c r="G65" s="6"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -1807,7 +2247,7 @@
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
+      <c r="G66" s="6"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -1824,7 +2264,7 @@
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
+      <c r="G67" s="6"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
@@ -1841,7 +2281,7 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
+      <c r="G68" s="6"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
@@ -1858,7 +2298,7 @@
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
+      <c r="G69" s="6"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
@@ -1873,7 +2313,7 @@
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
+      <c r="G70" s="6"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
@@ -1890,7 +2330,7 @@
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
+      <c r="G71" s="6"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -1907,7 +2347,7 @@
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
+      <c r="G72" s="6"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -1924,7 +2364,7 @@
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
+      <c r="G73" s="6"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -1941,7 +2381,7 @@
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
+      <c r="G74" s="6"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -1958,7 +2398,7 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
+      <c r="G75" s="6"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -1975,7 +2415,7 @@
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
+      <c r="G76" s="6"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -1992,7 +2432,7 @@
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
+      <c r="G77" s="6"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -2009,7 +2449,7 @@
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
+      <c r="G78" s="6"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -2026,7 +2466,7 @@
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
+      <c r="G79" s="6"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -2043,7 +2483,7 @@
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
+      <c r="G80" s="6"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -2060,7 +2500,7 @@
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
+      <c r="G81" s="6"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -2077,7 +2517,7 @@
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
+      <c r="G82" s="6"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -2092,7 +2532,7 @@
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
+      <c r="G83" s="6"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -2109,7 +2549,7 @@
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
+      <c r="G84" s="6"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -2126,7 +2566,7 @@
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
+      <c r="G85" s="6"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -2141,7 +2581,7 @@
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
+      <c r="G86" s="6"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -2158,7 +2598,7 @@
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
+      <c r="G87" s="6"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -2175,7 +2615,7 @@
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
+      <c r="G88" s="6"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -2192,7 +2632,7 @@
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
+      <c r="G89" s="6"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
@@ -2209,7 +2649,7 @@
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
+      <c r="G90" s="6"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
@@ -2226,7 +2666,7 @@
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
+      <c r="G91" s="6"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
@@ -2243,7 +2683,7 @@
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
+      <c r="G92" s="6"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -2260,7 +2700,7 @@
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
+      <c r="G93" s="6"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
@@ -2277,7 +2717,7 @@
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
+      <c r="G94" s="6"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
@@ -2294,7 +2734,7 @@
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
+      <c r="G95" s="6"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
@@ -2311,7 +2751,7 @@
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
+      <c r="G96" s="6"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -2328,7 +2768,7 @@
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
+      <c r="G97" s="6"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
@@ -2345,7 +2785,7 @@
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
+      <c r="G98" s="6"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -2362,7 +2802,7 @@
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
+      <c r="G99" s="6"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -2379,7 +2819,7 @@
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
+      <c r="G100" s="6"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -2394,7 +2834,7 @@
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
+      <c r="G101" s="6"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -2409,7 +2849,7 @@
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
+      <c r="G102" s="6"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -2422,7 +2862,7 @@
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
+      <c r="G103" s="6"/>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B244F6B-3B1B-4AE6-9861-DAB23610CAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DA3B85-5D9E-4177-B285-6507C93CDEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="139">
   <si>
     <t>Ejer</t>
   </si>
@@ -408,6 +408,51 @@
   </si>
   <si>
     <t>1m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aage Kragh Sørensen </t>
+  </si>
+  <si>
+    <t>8b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pihlkjær Jacobsen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9c -30g - 30f </t>
+  </si>
+  <si>
+    <t>8778 m2</t>
+  </si>
+  <si>
+    <t>Solbakken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristian Skøt Andersen </t>
+  </si>
+  <si>
+    <t>4p - 3i - 10 e</t>
+  </si>
+  <si>
+    <t>Skibbyvej</t>
+  </si>
+  <si>
+    <t>Andreas Maagaard Christiansen</t>
+  </si>
+  <si>
+    <t>13p</t>
+  </si>
+  <si>
+    <t>Niels Christian Christiansen</t>
+  </si>
+  <si>
+    <t>4l</t>
+  </si>
+  <si>
+    <t>Johannes Olsens</t>
+  </si>
+  <si>
+    <t>4m</t>
   </si>
 </sst>
 </file>
@@ -1784,11 +1829,17 @@
       <c r="B39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
+      <c r="C39" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="6"/>
+      <c r="G39" s="6">
+        <v>1928</v>
+      </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -1801,15 +1852,21 @@
       <c r="B40" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
+      <c r="C40" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="6"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
+      <c r="K40" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
@@ -1818,15 +1875,27 @@
       <c r="B41" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="C41" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="F41" s="1"/>
-      <c r="G41" s="6"/>
+      <c r="G41" s="6">
+        <v>1932</v>
+      </c>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+      <c r="I41" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
+      <c r="K41" s="1">
+        <v>7716</v>
+      </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
@@ -1835,15 +1904,21 @@
       <c r="B42" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
+      <c r="C42" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="6"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
+      <c r="K42" s="1">
+        <v>6800</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
@@ -1852,11 +1927,17 @@
       <c r="B43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
+      <c r="C43" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="6"/>
+      <c r="G43" s="6">
+        <v>1937</v>
+      </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -1869,11 +1950,19 @@
       <c r="B44" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="C44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="F44" s="1"/>
-      <c r="G44" s="6"/>
+      <c r="G44" s="6">
+        <v>1943</v>
+      </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DA3B85-5D9E-4177-B285-6507C93CDEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CD3DD1-7FF3-452C-8259-F3D4B9B66D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="155">
   <si>
     <t>Ejer</t>
   </si>
@@ -453,6 +453,54 @@
   </si>
   <si>
     <t>4m</t>
+  </si>
+  <si>
+    <t>Hans Eskerod</t>
+  </si>
+  <si>
+    <t>1n - 1f</t>
+  </si>
+  <si>
+    <t>16 bm</t>
+  </si>
+  <si>
+    <t>N. Staltzers</t>
+  </si>
+  <si>
+    <t>3009 m2</t>
+  </si>
+  <si>
+    <t>Ceres</t>
+  </si>
+  <si>
+    <t>Frode Kjær</t>
+  </si>
+  <si>
+    <t>1k - 13o</t>
+  </si>
+  <si>
+    <t>Østhjørnet af Aarslev Nordskov</t>
+  </si>
+  <si>
+    <t>Sine Jessen Jensen</t>
+  </si>
+  <si>
+    <t>3b - 3c</t>
+  </si>
+  <si>
+    <t>Helge Harmsen</t>
+  </si>
+  <si>
+    <t>4a - 4o - 11q</t>
+  </si>
+  <si>
+    <t>Rosenlund</t>
+  </si>
+  <si>
+    <t>A. C Andersen</t>
+  </si>
+  <si>
+    <t>12 ao</t>
   </si>
 </sst>
 </file>
@@ -1975,32 +2023,40 @@
       <c r="B45" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
+      <c r="C45" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="6"/>
+      <c r="G45" s="6">
+        <v>1897</v>
+      </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
+      <c r="B46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
@@ -2009,15 +2065,21 @@
       <c r="B47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
+      <c r="C47" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="6"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
+      <c r="K47" s="1" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
@@ -2026,13 +2088,23 @@
       <c r="B48" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+      <c r="C48" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F48" s="1"/>
-      <c r="G48" s="6"/>
+      <c r="G48" s="6">
+        <v>1902</v>
+      </c>
       <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="I48" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
@@ -2043,11 +2115,17 @@
       <c r="B49" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
+      <c r="C49" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-      <c r="G49" s="6"/>
+      <c r="G49" s="6">
+        <v>1942</v>
+      </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -2060,32 +2138,44 @@
       <c r="B50" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
+      <c r="C50" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-      <c r="G50" s="6"/>
+      <c r="G50" s="6">
+        <v>1954</v>
+      </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
+      <c r="A51" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
+      <c r="B51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="1">

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CD3DD1-7FF3-452C-8259-F3D4B9B66D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC4EE4F-13EA-4CA2-9257-D82A45F2D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="296">
   <si>
     <t>Ejer</t>
   </si>
@@ -501,6 +501,429 @@
   </si>
   <si>
     <t>12 ao</t>
+  </si>
+  <si>
+    <t>Hans Broge</t>
+  </si>
+  <si>
+    <t>11h</t>
+  </si>
+  <si>
+    <t>Det var ikke et gartneri</t>
+  </si>
+  <si>
+    <t>36- 15b - 5c. M.fl</t>
+  </si>
+  <si>
+    <t>Mortiz Rudolph Koppel</t>
+  </si>
+  <si>
+    <t>Det var ikke et gartneri men en privat have</t>
+  </si>
+  <si>
+    <t>Edwin Fredleif Rahr</t>
+  </si>
+  <si>
+    <t>5p</t>
+  </si>
+  <si>
+    <t>Endnu en velhavende mand, men en som kan betragtes som gartner, da han deltog i flere gartnerudstillinger</t>
+  </si>
+  <si>
+    <t>H. De Linde</t>
+  </si>
+  <si>
+    <t>H. De Lindes Gartneri</t>
+  </si>
+  <si>
+    <t>5f -29b.</t>
+  </si>
+  <si>
+    <t>7582 m2 og 2 ha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Greisens </t>
+  </si>
+  <si>
+    <t>A. Greisens Gartneri</t>
+  </si>
+  <si>
+    <t>9ha 426m2</t>
+  </si>
+  <si>
+    <t>21a-  21d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anders Kristiansen </t>
+  </si>
+  <si>
+    <t>16c</t>
+  </si>
+  <si>
+    <t>A. Jeppesen</t>
+  </si>
+  <si>
+    <t>Holmstruphøj</t>
+  </si>
+  <si>
+    <t>16i</t>
+  </si>
+  <si>
+    <t>2 ½ ha</t>
+  </si>
+  <si>
+    <t>Jørgen Schousen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kan ikke finde ham </t>
+  </si>
+  <si>
+    <t>Ingeborg Bach</t>
+  </si>
+  <si>
+    <t>Ingeborg Bachs Gartneri</t>
+  </si>
+  <si>
+    <t>2 ha, 7664 m2</t>
+  </si>
+  <si>
+    <t>16b</t>
+  </si>
+  <si>
+    <t>Laurits Sejer Larsen</t>
+  </si>
+  <si>
+    <t>16h - 16k</t>
+  </si>
+  <si>
+    <t>Udstykket fra 16h</t>
+  </si>
+  <si>
+    <t>Kirstine Knudsen</t>
+  </si>
+  <si>
+    <t>Jørgen Fruelunf</t>
+  </si>
+  <si>
+    <t>Asmus Rasmussen og  Vagn Christian Rasmussen</t>
+  </si>
+  <si>
+    <t>6000 m2 og 2½ ha</t>
+  </si>
+  <si>
+    <t>Gartneriet Nyvang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440 m2 </t>
+  </si>
+  <si>
+    <t>H. Schroll Christiansen og senere Harald Schroll Christiansen</t>
+  </si>
+  <si>
+    <t>J. Mortensen</t>
+  </si>
+  <si>
+    <t>Vidt Skue</t>
+  </si>
+  <si>
+    <t>16q</t>
+  </si>
+  <si>
+    <t>5b</t>
+  </si>
+  <si>
+    <t>1ha 6549 m2</t>
+  </si>
+  <si>
+    <t>Poul Andersen</t>
+  </si>
+  <si>
+    <t>4h</t>
+  </si>
+  <si>
+    <t>Anders Sørensen</t>
+  </si>
+  <si>
+    <t>Anders Sørensens Gartneri</t>
+  </si>
+  <si>
+    <t>True 29c - Aarslev 1d, 1g</t>
+  </si>
+  <si>
+    <t>3ha 6907m2 - Anmærkning punkterne er placeret forkert på de fysiske kort.</t>
+  </si>
+  <si>
+    <t>1l</t>
+  </si>
+  <si>
+    <t>1h 6548m2</t>
+  </si>
+  <si>
+    <t>Tage Laursens Gartneri</t>
+  </si>
+  <si>
+    <t>Tage Laursens</t>
+  </si>
+  <si>
+    <t>1ae, 1ak</t>
+  </si>
+  <si>
+    <t>2 ha, 9830 m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H. Kaysens </t>
+  </si>
+  <si>
+    <t>H. Kaysens Gartneri</t>
+  </si>
+  <si>
+    <t>3.8 ha</t>
+  </si>
+  <si>
+    <t>9b.</t>
+  </si>
+  <si>
+    <t>P.J Sørensen</t>
+  </si>
+  <si>
+    <t>P.J Sørensens Gartneri</t>
+  </si>
+  <si>
+    <t>1ha, 4650 m2</t>
+  </si>
+  <si>
+    <t>4b</t>
+  </si>
+  <si>
+    <t>Søren Eskesens Gartneri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1ha, 1032 m2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Søren Eskesens </t>
+  </si>
+  <si>
+    <t>Morten Eriksen</t>
+  </si>
+  <si>
+    <t>1d - True 23b</t>
+  </si>
+  <si>
+    <t>Lærkelund a/s</t>
+  </si>
+  <si>
+    <t>3b-3d-3e-3k.3m</t>
+  </si>
+  <si>
+    <t>Rosalina a/s</t>
+  </si>
+  <si>
+    <t>3f-3d-3e-3k-3m</t>
+  </si>
+  <si>
+    <t>Erik Balle</t>
+  </si>
+  <si>
+    <t>14l</t>
+  </si>
+  <si>
+    <t>grundlagt 1935 - overtaget 1948</t>
+  </si>
+  <si>
+    <t>E. Balle</t>
+  </si>
+  <si>
+    <t>Hejredalsvej 6</t>
+  </si>
+  <si>
+    <t>Frøken Kirstine Schmith</t>
+  </si>
+  <si>
+    <t>14k</t>
+  </si>
+  <si>
+    <t>Marius Jensen</t>
+  </si>
+  <si>
+    <t>Marius Jensens Handelsgartneri</t>
+  </si>
+  <si>
+    <t>9g</t>
+  </si>
+  <si>
+    <t>Vilhelm Nielsen</t>
+  </si>
+  <si>
+    <t>Fuglsang</t>
+  </si>
+  <si>
+    <t>H. Pedersens Handelsgartneri</t>
+  </si>
+  <si>
+    <t>5 ½ ha</t>
+  </si>
+  <si>
+    <t>Herman Pedersen</t>
+  </si>
+  <si>
+    <t>9d</t>
+  </si>
+  <si>
+    <t>4i</t>
+  </si>
+  <si>
+    <t>Carlo Blicher</t>
+  </si>
+  <si>
+    <t>Østergaard</t>
+  </si>
+  <si>
+    <t>GASA</t>
+  </si>
+  <si>
+    <t>Blomstervej 8 Tilst</t>
+  </si>
+  <si>
+    <t>Stillinggaard</t>
+  </si>
+  <si>
+    <t>Herlov Harmsen</t>
+  </si>
+  <si>
+    <t>14b</t>
+  </si>
+  <si>
+    <t>11ha</t>
+  </si>
+  <si>
+    <t>Skjoldhøjgaard</t>
+  </si>
+  <si>
+    <t>Jens Harmsen</t>
+  </si>
+  <si>
+    <t>21a - 21d</t>
+  </si>
+  <si>
+    <t>9ha, 426 m2</t>
+  </si>
+  <si>
+    <t>Ingemann Petersen</t>
+  </si>
+  <si>
+    <t>12an</t>
+  </si>
+  <si>
+    <t>Skovly</t>
+  </si>
+  <si>
+    <t>1 1/4 ha</t>
+  </si>
+  <si>
+    <t>Rasmus Andersen</t>
+  </si>
+  <si>
+    <t>12 am.</t>
+  </si>
+  <si>
+    <t>Skovbakkevej</t>
+  </si>
+  <si>
+    <t>Thor Petersen</t>
+  </si>
+  <si>
+    <t>23b</t>
+  </si>
+  <si>
+    <t>Edwin Rahrs Vej 56</t>
+  </si>
+  <si>
+    <t>Vaabenlund - Planteskole</t>
+  </si>
+  <si>
+    <t>Aage Petersen</t>
+  </si>
+  <si>
+    <t>12 al, 10 as</t>
+  </si>
+  <si>
+    <t>Sven Hansen</t>
+  </si>
+  <si>
+    <t>5q-5m</t>
+  </si>
+  <si>
+    <t>11c m.fl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erik Hejredeal </t>
+  </si>
+  <si>
+    <t>Hejredal</t>
+  </si>
+  <si>
+    <t>1bi m.fl</t>
+  </si>
+  <si>
+    <t>Bækkelund</t>
+  </si>
+  <si>
+    <t>Blev senere anlægsgartner</t>
+  </si>
+  <si>
+    <t>14g m fl.</t>
+  </si>
+  <si>
+    <t>Blomsterdekoratør Nielsen</t>
+  </si>
+  <si>
+    <t>Tidligere medarbejder hos blomsterhandler Abel</t>
+  </si>
+  <si>
+    <t>J.P Ibsen Sørensen</t>
+  </si>
+  <si>
+    <t>Aarslev Handelsgartneri</t>
+  </si>
+  <si>
+    <t>4k &amp; 31a</t>
+  </si>
+  <si>
+    <t>Hugo Dybdal Jensen</t>
+  </si>
+  <si>
+    <t>Ørvadsvej</t>
+  </si>
+  <si>
+    <t>C. Ussings Handelsgartneri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. Ussings </t>
+  </si>
+  <si>
+    <t>Voldbæk</t>
+  </si>
+  <si>
+    <t>Ingen adresse</t>
+  </si>
+  <si>
+    <t>Jens Arne Jørgensen</t>
+  </si>
+  <si>
+    <t>4c</t>
+  </si>
+  <si>
+    <t>1947-1951</t>
+  </si>
+  <si>
+    <t>Svend Aage Ballgaard</t>
+  </si>
+  <si>
+    <t>4l &amp; 4æ</t>
+  </si>
+  <si>
+    <t>Medlemsliste</t>
   </si>
 </sst>
 </file>
@@ -576,7 +999,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -597,6 +1020,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1941,7 +2365,7 @@
         <v>129</v>
       </c>
       <c r="J41" s="1"/>
-      <c r="K41" s="1">
+      <c r="K41" s="6">
         <v>7716</v>
       </c>
     </row>
@@ -1964,7 +2388,7 @@
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="1">
+      <c r="K42" s="6">
         <v>6800</v>
       </c>
     </row>
@@ -2178,21 +2602,27 @@
       <c r="K51" s="5"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
+      <c r="B52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
@@ -2201,15 +2631,21 @@
       <c r="B53" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
+      <c r="C53" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="6"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
+      <c r="K53" s="1" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
@@ -2218,15 +2654,21 @@
       <c r="B54" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+      <c r="C54" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="6"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
+      <c r="K54" s="1" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
@@ -2235,15 +2677,23 @@
       <c r="B55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
+      <c r="C55" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="6"/>
       <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="I55" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
+      <c r="K55" s="1" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
@@ -2252,15 +2702,23 @@
       <c r="B56" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+      <c r="C56" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="6"/>
       <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
+      <c r="I56" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
+      <c r="K56" s="1" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
@@ -2269,11 +2727,17 @@
       <c r="B57" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
+      <c r="C57" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>173</v>
+      </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="6"/>
+      <c r="G57" s="6">
+        <v>1956</v>
+      </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -2286,15 +2750,25 @@
       <c r="B58" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
+      <c r="C58" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="6"/>
+      <c r="G58" s="6">
+        <v>1926</v>
+      </c>
       <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
+      <c r="I58" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
@@ -2303,32 +2777,42 @@
       <c r="B59" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
+      <c r="C59" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="6"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
+      <c r="I59" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
+      <c r="K59" s="1" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
@@ -2337,15 +2821,23 @@
       <c r="B61" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
+      <c r="C61" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="6"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
+      <c r="I61" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+      <c r="K61" s="1" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
@@ -2354,11 +2846,17 @@
       <c r="B62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+      <c r="C62" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="6"/>
+      <c r="G62" s="6">
+        <v>1948</v>
+      </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -2371,8 +2869,12 @@
       <c r="B63" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
+      <c r="C63" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="6"/>
@@ -2388,8 +2890,12 @@
       <c r="B64" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
+      <c r="C64" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="6"/>
@@ -2405,15 +2911,23 @@
       <c r="B65" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
+      <c r="C65" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="6"/>
+      <c r="G65" s="6">
+        <v>1961</v>
+      </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
+      <c r="K65" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
@@ -2422,15 +2936,25 @@
       <c r="B66" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
+      <c r="C66" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="6"/>
+      <c r="G66" s="6">
+        <v>1932</v>
+      </c>
       <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
+      <c r="I66" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
+      <c r="K66" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
@@ -2439,15 +2963,23 @@
       <c r="B67" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
+      <c r="C67" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="6"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
+      <c r="I67" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
+      <c r="K67" s="1" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
@@ -2456,47 +2988,67 @@
       <c r="B68" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
+      <c r="C68" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>200</v>
+      </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="6"/>
+      <c r="G68" s="6">
+        <v>1939</v>
+      </c>
       <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
+      <c r="I68" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
@@ -2505,15 +3057,23 @@
       <c r="B71" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
+      <c r="C71" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="6"/>
       <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
+      <c r="I71" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
+      <c r="K71" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
@@ -2522,15 +3082,23 @@
       <c r="B72" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
+      <c r="C72" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="6"/>
       <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
+      <c r="I72" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
+      <c r="K72" s="1" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
@@ -2539,15 +3107,23 @@
       <c r="B73" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
+      <c r="C73" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="6"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
+      <c r="I73" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
+      <c r="K73" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
@@ -2556,15 +3132,23 @@
       <c r="B74" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
+      <c r="C74" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="6"/>
       <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
+      <c r="I74" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
+      <c r="K74" s="1" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
@@ -2573,8 +3157,12 @@
       <c r="B75" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
+      <c r="C75" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>223</v>
+      </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="6"/>
@@ -2591,12 +3179,18 @@
         <v>18</v>
       </c>
       <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
+      <c r="D76" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="F76" s="1"/>
       <c r="G76" s="6"/>
       <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
+      <c r="I76" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
@@ -2608,12 +3202,18 @@
         <v>15</v>
       </c>
       <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
+      <c r="D77" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="F77" s="1"/>
       <c r="G77" s="6"/>
       <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
+      <c r="I77" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
     </row>
@@ -2624,13 +3224,23 @@
       <c r="B78" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
+      <c r="C78" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="F78" s="1"/>
-      <c r="G78" s="6"/>
+      <c r="G78" s="6" t="s">
+        <v>230</v>
+      </c>
       <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
+      <c r="I78" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
     </row>
@@ -2641,8 +3251,12 @@
       <c r="B79" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
+      <c r="C79" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>234</v>
+      </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="6"/>
@@ -2658,32 +3272,46 @@
       <c r="B80" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
+      <c r="C80" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="6"/>
+      <c r="G80" s="6">
+        <v>1899</v>
+      </c>
       <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
+      <c r="I80" s="1" t="s">
+        <v>236</v>
+      </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A81" s="1">
+      <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
+      <c r="C81" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F81" s="2"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
@@ -2692,23 +3320,39 @@
       <c r="B82" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
+      <c r="C82" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>243</v>
+      </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="6"/>
+      <c r="G82" s="6">
+        <v>1899</v>
+      </c>
       <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
+      <c r="I82" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
+      <c r="K82" s="1" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
+      <c r="B83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="6"/>
@@ -2724,8 +3368,12 @@
       <c r="B84" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
+      <c r="C84" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>200</v>
+      </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="6"/>
@@ -2741,9 +3389,13 @@
       <c r="B85" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C85" s="1"/>
+      <c r="C85" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
+      <c r="E85" s="1" t="s">
+        <v>248</v>
+      </c>
       <c r="F85" s="1"/>
       <c r="G85" s="6"/>
       <c r="H85" s="1"/>
@@ -2755,16 +3407,28 @@
       <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
+      <c r="B86" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="6"/>
+      <c r="G86" s="6">
+        <v>1944</v>
+      </c>
       <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
+      <c r="I86" s="1" t="s">
+        <v>249</v>
+      </c>
       <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
+      <c r="K86" s="1" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
@@ -2773,15 +3437,25 @@
       <c r="B87" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
+      <c r="C87" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>255</v>
+      </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="6"/>
+      <c r="G87" s="6">
+        <v>1941</v>
+      </c>
       <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
+      <c r="I87" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
+      <c r="K87" s="1" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
@@ -2790,8 +3464,12 @@
       <c r="B88" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
+      <c r="C88" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="6"/>
@@ -2807,15 +3485,27 @@
       <c r="B89" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
+      <c r="C89" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="F89" s="1"/>
-      <c r="G89" s="6"/>
+      <c r="G89" s="6">
+        <v>1909</v>
+      </c>
       <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
+      <c r="I89" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
+      <c r="K89" s="1" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
@@ -2824,13 +3514,23 @@
       <c r="B90" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
+      <c r="C90" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>266</v>
+      </c>
       <c r="F90" s="1"/>
-      <c r="G90" s="6"/>
+      <c r="G90" s="6">
+        <v>1944</v>
+      </c>
       <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
+      <c r="I90" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
     </row>
@@ -2841,11 +3541,17 @@
       <c r="B91" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
+      <c r="C91" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
-      <c r="G91" s="6"/>
+      <c r="G91" s="6">
+        <v>1933</v>
+      </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
@@ -2858,8 +3564,12 @@
       <c r="B92" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
+      <c r="C92" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="6"/>
@@ -2875,13 +3585,19 @@
       <c r="B93" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
+      <c r="C93" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="6"/>
       <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
+      <c r="I93" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
     </row>
@@ -2892,15 +3608,21 @@
       <c r="B94" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
+      <c r="C94" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>275</v>
+      </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="6"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
-      <c r="K94" s="1"/>
+      <c r="K94" s="1" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
@@ -2909,15 +3631,21 @@
       <c r="B95" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
+      <c r="C95" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="6"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
+      <c r="K95" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
@@ -2926,13 +3654,21 @@
       <c r="B96" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
+      <c r="C96" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>283</v>
+      </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="6"/>
+      <c r="G96" s="6">
+        <v>1931</v>
+      </c>
       <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
+      <c r="I96" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
     </row>
@@ -2943,32 +3679,48 @@
       <c r="B97" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
+      <c r="C97" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>285</v>
+      </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
-      <c r="G97" s="6"/>
+      <c r="G97" s="6">
+        <v>1954</v>
+      </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>97</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1"/>
-      <c r="K98" s="1"/>
+      <c r="B98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" s="3">
+        <v>1920</v>
+      </c>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
@@ -2977,11 +3729,17 @@
       <c r="B99" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
+      <c r="C99" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="6"/>
+      <c r="G99" s="6" t="s">
+        <v>292</v>
+      </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
@@ -2994,11 +3752,17 @@
       <c r="B100" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
+      <c r="C100" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>294</v>
+      </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="6"/>
+      <c r="G100" s="6">
+        <v>1938</v>
+      </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -3008,7 +3772,9 @@
       <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="B101" s="1"/>
+      <c r="B101" s="1" t="s">
+        <v>295</v>
+      </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIS\Github Update\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC4EE4F-13EA-4CA2-9257-D82A45F2D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7BFC0C-4C26-4679-B603-DAA68F95616E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="332">
   <si>
     <t>Ejer</t>
   </si>
@@ -924,6 +924,114 @@
   </si>
   <si>
     <t>Medlemsliste</t>
+  </si>
+  <si>
+    <t>56.151908, 10.121680</t>
+  </si>
+  <si>
+    <t>56.148938, 10.126916</t>
+  </si>
+  <si>
+    <t>56.148125, 10.126643</t>
+  </si>
+  <si>
+    <t>56.148896, 10.125157</t>
+  </si>
+  <si>
+    <t>56.149333, 10.115533</t>
+  </si>
+  <si>
+    <t>56.149319, 10.126372</t>
+  </si>
+  <si>
+    <t>56.151586, 10.123091</t>
+  </si>
+  <si>
+    <t>56.149292, 10.124097</t>
+  </si>
+  <si>
+    <t>56.149043, 10.124360</t>
+  </si>
+  <si>
+    <t>56.150310, 10.123625</t>
+  </si>
+  <si>
+    <t>56.150668, 10.121702</t>
+  </si>
+  <si>
+    <t>56.150534, 10.122485</t>
+  </si>
+  <si>
+    <t>56.150886, 10.121010</t>
+  </si>
+  <si>
+    <t>56.151374, 10.118617</t>
+  </si>
+  <si>
+    <t>56.153035, 10.110185</t>
+  </si>
+  <si>
+    <t>56.152013, 10.110174</t>
+  </si>
+  <si>
+    <t>56.152216, 10.112770</t>
+  </si>
+  <si>
+    <t>56.151215, 10.108076</t>
+  </si>
+  <si>
+    <t>56.152049, 10.114176</t>
+  </si>
+  <si>
+    <t>56.152342, 10.104037</t>
+  </si>
+  <si>
+    <t>56.153486, 10.092997</t>
+  </si>
+  <si>
+    <t>56.153797, 10.094590</t>
+  </si>
+  <si>
+    <t>56.154717, 10.089494</t>
+  </si>
+  <si>
+    <t>56.149016, 10.116633</t>
+  </si>
+  <si>
+    <t>56.149088, 10.118392</t>
+  </si>
+  <si>
+    <t>56.153074, 10.095749</t>
+  </si>
+  <si>
+    <t>56.152276, 10.095577</t>
+  </si>
+  <si>
+    <t>56.158792, 10.119503</t>
+  </si>
+  <si>
+    <t>56.157651, 10.117335</t>
+  </si>
+  <si>
+    <t>56.159521, 10.105534</t>
+  </si>
+  <si>
+    <t>56.158923, 10.085605</t>
+  </si>
+  <si>
+    <t>56.151810, 10.116820</t>
+  </si>
+  <si>
+    <t>56.154275, 10.118124</t>
+  </si>
+  <si>
+    <t>56.155781, 10.105024</t>
+  </si>
+  <si>
+    <t>56.152144, 10.124250</t>
+  </si>
+  <si>
+    <t>56.156124, 10.105963</t>
   </si>
 </sst>
 </file>
@@ -1356,20 +1464,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9410E6E1-B6FD-499D-B70E-01FA93ABCF11}">
   <dimension ref="A1:K103"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.81640625" customWidth="1"/>
-    <col min="3" max="3" width="26.54296875" customWidth="1"/>
-    <col min="4" max="4" width="28.1796875" customWidth="1"/>
-    <col min="5" max="6" width="17.26953125" customWidth="1"/>
-    <col min="7" max="7" width="21.54296875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="25.1796875" customWidth="1"/>
-    <col min="9" max="9" width="25.7265625" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" customWidth="1"/>
-    <col min="11" max="11" width="36.08984375" customWidth="1"/>
+    <col min="1" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="28.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="36.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1404,7 +1513,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1420,7 +1529,9 @@
       <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
@@ -1431,7 +1542,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1450,7 +1561,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1469,7 +1580,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1485,14 +1596,16 @@
       <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>301</v>
+      </c>
       <c r="G5" s="6"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1519,7 +1632,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1535,7 +1648,9 @@
       <c r="E7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>297</v>
+      </c>
       <c r="G7" s="7">
         <v>1902</v>
       </c>
@@ -1548,7 +1663,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1560,14 +1675,16 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>298</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1583,7 +1700,9 @@
       <c r="E9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="G9" s="6" t="s">
         <v>37</v>
       </c>
@@ -1594,7 +1713,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1608,7 +1727,9 @@
       <c r="E10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>300</v>
+      </c>
       <c r="G10" s="6">
         <v>1933</v>
       </c>
@@ -1621,7 +1742,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1648,7 +1769,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1675,7 +1796,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1700,7 +1821,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1716,7 +1837,9 @@
       <c r="E14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="G14" s="6"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
@@ -1725,7 +1848,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1741,14 +1864,16 @@
       <c r="E15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>303</v>
+      </c>
       <c r="G15" s="6"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1764,14 +1889,16 @@
       <c r="E16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>304</v>
+      </c>
       <c r="G16" s="6"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1787,14 +1914,16 @@
       <c r="E17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>305</v>
+      </c>
       <c r="G17" s="6"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1810,14 +1939,16 @@
       <c r="E18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>306</v>
+      </c>
       <c r="G18" s="8"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1833,14 +1964,16 @@
       <c r="E19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>307</v>
+      </c>
       <c r="G19" s="6"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1856,14 +1989,16 @@
       <c r="E20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>308</v>
+      </c>
       <c r="G20" s="6"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1879,14 +2014,16 @@
       <c r="E21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="1"/>
+      <c r="F21" s="1" t="s">
+        <v>309</v>
+      </c>
       <c r="G21" s="6"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1900,7 +2037,9 @@
         <v>76</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="F22" s="1" t="s">
+        <v>310</v>
+      </c>
       <c r="G22" s="6">
         <v>1921</v>
       </c>
@@ -1911,7 +2050,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1927,13 +2066,15 @@
       <c r="E23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="1"/>
+      <c r="F23" s="1" t="s">
+        <v>311</v>
+      </c>
       <c r="G23" s="6"/>
       <c r="H23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1949,7 +2090,9 @@
       <c r="E24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>312</v>
+      </c>
       <c r="G24" s="6"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
@@ -1960,7 +2103,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1976,7 +2119,9 @@
       <c r="E25" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="1"/>
+      <c r="F25" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="G25" s="6"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
@@ -1987,7 +2132,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1999,14 +2144,16 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="F26" s="2" t="s">
+        <v>314</v>
+      </c>
       <c r="G26" s="3"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -2020,14 +2167,16 @@
         <v>90</v>
       </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="F27" s="5" t="s">
+        <v>315</v>
+      </c>
       <c r="G27" s="8"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2043,7 +2192,9 @@
       <c r="E28" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>316</v>
+      </c>
       <c r="G28" s="6">
         <v>1914</v>
       </c>
@@ -2054,7 +2205,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2068,7 +2219,9 @@
       <c r="E29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>317</v>
+      </c>
       <c r="G29" s="6"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -2077,7 +2230,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2091,7 +2244,9 @@
         <v>99</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="F30" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="G30" s="6">
         <v>1936</v>
       </c>
@@ -2102,7 +2257,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2118,7 +2273,9 @@
       <c r="E31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>319</v>
+      </c>
       <c r="G31" s="6">
         <v>1957</v>
       </c>
@@ -2127,7 +2284,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2143,14 +2300,16 @@
       <c r="E32" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="1"/>
+      <c r="F32" s="1" t="s">
+        <v>320</v>
+      </c>
       <c r="G32" s="6"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2166,7 +2325,9 @@
       <c r="E33" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>321</v>
+      </c>
       <c r="G33" s="6"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
@@ -2177,7 +2338,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2193,14 +2354,16 @@
       <c r="E34" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="G34" s="6"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2216,7 +2379,9 @@
       <c r="E35" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>323</v>
+      </c>
       <c r="G35" s="6">
         <v>1870</v>
       </c>
@@ -2227,7 +2392,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2239,14 +2404,16 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
+      <c r="F36" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="G36" s="3"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2260,7 +2427,9 @@
         <v>120</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
+      <c r="F37" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="G37" s="6"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="s">
@@ -2271,7 +2440,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2294,7 +2463,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2317,7 +2486,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2340,7 +2509,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2369,7 +2538,7 @@
         <v>7716</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2392,7 +2561,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2415,7 +2584,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -2440,7 +2609,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -2454,7 +2623,9 @@
         <v>140</v>
       </c>
       <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>326</v>
+      </c>
       <c r="G45" s="6">
         <v>1897</v>
       </c>
@@ -2463,7 +2634,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2482,7 +2653,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2496,7 +2667,9 @@
         <v>141</v>
       </c>
       <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>327</v>
+      </c>
       <c r="G47" s="6"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -2505,7 +2678,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2532,7 +2705,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -2555,7 +2728,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2578,7 +2751,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -2592,7 +2765,9 @@
         <v>154</v>
       </c>
       <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+      <c r="F51" s="5" t="s">
+        <v>328</v>
+      </c>
       <c r="G51" s="8"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
@@ -2601,7 +2776,7 @@
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2615,7 +2790,9 @@
         <v>156</v>
       </c>
       <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
+      <c r="F52" s="2" t="s">
+        <v>329</v>
+      </c>
       <c r="G52" s="3"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -2624,7 +2801,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2638,7 +2815,9 @@
         <v>158</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
+      <c r="F53" s="1" t="s">
+        <v>330</v>
+      </c>
       <c r="G53" s="6"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -2647,7 +2826,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -2661,7 +2840,9 @@
         <v>162</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>331</v>
+      </c>
       <c r="G54" s="6"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -2670,7 +2851,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2695,7 +2876,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2720,7 +2901,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2743,7 +2924,7 @@
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2770,7 +2951,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2795,7 +2976,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2814,7 +2995,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2839,7 +3020,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2862,7 +3043,7 @@
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -2883,7 +3064,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2904,7 +3085,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2929,7 +3110,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -2956,7 +3137,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -2981,7 +3162,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3006,7 +3187,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3029,7 +3210,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3050,7 +3231,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3075,7 +3256,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3100,7 +3281,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -3125,7 +3306,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -3150,7 +3331,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -3171,7 +3352,7 @@
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -3194,7 +3375,7 @@
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -3217,7 +3398,7 @@
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -3244,7 +3425,7 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -3265,7 +3446,7 @@
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -3290,7 +3471,7 @@
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3313,7 +3494,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -3340,7 +3521,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -3361,7 +3542,7 @@
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -3382,7 +3563,7 @@
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -3403,7 +3584,7 @@
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -3430,7 +3611,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -3457,7 +3638,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -3478,7 +3659,7 @@
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -3507,7 +3688,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -3534,7 +3715,7 @@
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -3557,7 +3738,7 @@
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -3578,7 +3759,7 @@
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -3601,7 +3782,7 @@
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -3624,7 +3805,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -3647,7 +3828,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -3672,7 +3853,7 @@
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -3695,7 +3876,7 @@
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -3722,7 +3903,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -3745,7 +3926,7 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -3768,7 +3949,7 @@
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -3785,7 +3966,7 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -3800,7 +3981,7 @@
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIS\Github Update\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7BFC0C-4C26-4679-B603-DAA68F95616E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0237529D-9C12-44A9-A4C2-6F528D3A3FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="359">
   <si>
     <t>Ejer</t>
   </si>
@@ -926,9 +926,6 @@
     <t>Medlemsliste</t>
   </si>
   <si>
-    <t>56.151908, 10.121680</t>
-  </si>
-  <si>
     <t>56.148938, 10.126916</t>
   </si>
   <si>
@@ -1032,6 +1029,90 @@
   </si>
   <si>
     <t>56.156124, 10.105963</t>
+  </si>
+  <si>
+    <t>56.150331, 10.076845</t>
+  </si>
+  <si>
+    <t>56.149913, 10.080503</t>
+  </si>
+  <si>
+    <t>56.149533, 10.083373</t>
+  </si>
+  <si>
+    <t>56.149147, 10.065612</t>
+  </si>
+  <si>
+    <t>56.148723, 10.064603</t>
+  </si>
+  <si>
+    <t>56.149070, 10.066781</t>
+  </si>
+  <si>
+    <t>56.155278, 10.085610</t>
+  </si>
+  <si>
+    <t>56.156425, 10.084237</t>
+  </si>
+  <si>
+    <t>56.148059, 10.057704</t>
+  </si>
+  <si>
+    <t>56.148974, 10.069238</t>
+  </si>
+  <si>
+    <t>56.147020, 10.055645</t>
+  </si>
+  <si>
+    <t>56.146416, 10.055966</t>
+  </si>
+  <si>
+    <t>56.148333, 10.063863</t>
+  </si>
+  <si>
+    <t>56.147243, 10.061857</t>
+  </si>
+  <si>
+    <t>56.148657, 10.083679</t>
+  </si>
+  <si>
+    <t>56.145068, 10.058863</t>
+  </si>
+  <si>
+    <t>56.152004, 10.122382</t>
+  </si>
+  <si>
+    <t>56.152169, 10.121476</t>
+  </si>
+  <si>
+    <t>56.158428, 10.107397</t>
+  </si>
+  <si>
+    <t>56.159383, 10.107955</t>
+  </si>
+  <si>
+    <t>56.160267, 10.108706</t>
+  </si>
+  <si>
+    <t>56.164819, 10.115722</t>
+  </si>
+  <si>
+    <t>56.154926, 10.106496</t>
+  </si>
+  <si>
+    <t>56.158308, 10.123565</t>
+  </si>
+  <si>
+    <t>56.156415, 10.123812</t>
+  </si>
+  <si>
+    <t>56.159306, 10.121237</t>
+  </si>
+  <si>
+    <t>56.153905, 10.120783</t>
+  </si>
+  <si>
+    <t>56.153553, 10.118423</t>
   </si>
 </sst>
 </file>
@@ -1464,21 +1545,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9410E6E1-B6FD-499D-B70E-01FA93ABCF11}">
   <dimension ref="A1:K103"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="1" max="2" width="14.81640625" customWidth="1"/>
+    <col min="3" max="3" width="26.54296875" customWidth="1"/>
+    <col min="4" max="4" width="28.1796875" customWidth="1"/>
+    <col min="5" max="5" width="17.26953125" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="11" max="11" width="36.140625" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="25.1796875" customWidth="1"/>
+    <col min="9" max="9" width="25.7265625" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" customWidth="1"/>
+    <col min="11" max="11" width="36.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1513,7 +1594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1530,7 +1611,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>296</v>
+        <v>348</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>8</v>
@@ -1542,7 +1623,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1561,7 +1642,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1580,7 +1661,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1597,7 +1678,7 @@
         <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="1"/>
@@ -1605,7 +1686,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1632,7 +1713,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1649,7 +1730,7 @@
         <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G7" s="7">
         <v>1902</v>
@@ -1663,7 +1744,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1676,7 +1757,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
@@ -1684,7 +1765,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1701,7 +1782,7 @@
         <v>38</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>37</v>
@@ -1713,7 +1794,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1728,7 +1809,7 @@
         <v>41</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G10" s="6">
         <v>1933</v>
@@ -1742,7 +1823,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1769,7 +1850,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1796,7 +1877,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1821,7 +1902,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1838,7 +1919,7 @@
         <v>56</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="1"/>
@@ -1848,7 +1929,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1865,7 +1946,7 @@
         <v>57</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="1"/>
@@ -1873,7 +1954,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1890,7 +1971,7 @@
         <v>61</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="1"/>
@@ -1898,7 +1979,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1915,7 +1996,7 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="1"/>
@@ -1923,7 +2004,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1940,7 +2021,7 @@
         <v>38</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="5"/>
@@ -1948,7 +2029,7 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1965,7 +2046,7 @@
         <v>38</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="1"/>
@@ -1973,7 +2054,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1990,7 +2071,7 @@
         <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="1"/>
@@ -1998,7 +2079,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2015,7 +2096,7 @@
         <v>38</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="1"/>
@@ -2023,7 +2104,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2038,7 +2119,7 @@
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G22" s="6">
         <v>1921</v>
@@ -2050,7 +2131,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2067,14 +2148,14 @@
         <v>78</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2091,7 +2172,7 @@
         <v>38</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="1"/>
@@ -2103,7 +2184,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2120,7 +2201,7 @@
         <v>86</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="1"/>
@@ -2132,7 +2213,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2145,7 +2226,7 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="2"/>
@@ -2153,7 +2234,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -2168,7 +2249,7 @@
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="5"/>
@@ -2176,7 +2257,7 @@
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2193,7 +2274,7 @@
         <v>91</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G28" s="6">
         <v>1914</v>
@@ -2205,7 +2286,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2220,7 +2301,7 @@
         <v>96</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="1"/>
@@ -2230,7 +2311,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2245,7 +2326,7 @@
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G30" s="6">
         <v>1936</v>
@@ -2257,7 +2338,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2274,7 +2355,7 @@
         <v>38</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G31" s="6">
         <v>1957</v>
@@ -2284,7 +2365,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2301,7 +2382,7 @@
         <v>38</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="1"/>
@@ -2309,7 +2390,7 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2326,7 +2407,7 @@
         <v>107</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="1"/>
@@ -2338,7 +2419,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2355,7 +2436,7 @@
         <v>112</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="1"/>
@@ -2363,7 +2444,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2380,7 +2461,7 @@
         <v>115</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G35" s="6">
         <v>1870</v>
@@ -2392,7 +2473,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2405,7 +2486,7 @@
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="2"/>
@@ -2413,7 +2494,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2428,7 +2509,7 @@
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="1"/>
@@ -2440,7 +2521,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2454,7 +2535,9 @@
         <v>123</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+      <c r="F38" s="1" t="s">
+        <v>331</v>
+      </c>
       <c r="G38" s="6">
         <v>1942</v>
       </c>
@@ -2463,7 +2546,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2477,7 +2560,9 @@
         <v>125</v>
       </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>333</v>
+      </c>
       <c r="G39" s="6">
         <v>1928</v>
       </c>
@@ -2486,7 +2571,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2500,7 +2585,9 @@
         <v>127</v>
       </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
+      <c r="F40" s="1" t="s">
+        <v>332</v>
+      </c>
       <c r="G40" s="6"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2509,7 +2596,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2525,7 +2612,9 @@
       <c r="E41" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>334</v>
+      </c>
       <c r="G41" s="6">
         <v>1932</v>
       </c>
@@ -2538,7 +2627,7 @@
         <v>7716</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2552,7 +2641,9 @@
         <v>134</v>
       </c>
       <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="F42" s="1" t="s">
+        <v>337</v>
+      </c>
       <c r="G42" s="6"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -2561,7 +2652,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2575,7 +2666,9 @@
         <v>136</v>
       </c>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>335</v>
+      </c>
       <c r="G43" s="6">
         <v>1937</v>
       </c>
@@ -2584,7 +2677,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -2600,7 +2693,9 @@
       <c r="E44" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>336</v>
+      </c>
       <c r="G44" s="6">
         <v>1943</v>
       </c>
@@ -2609,7 +2704,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -2624,7 +2719,7 @@
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G45" s="6">
         <v>1897</v>
@@ -2634,7 +2729,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2653,7 +2748,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2668,7 +2763,7 @@
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="1"/>
@@ -2678,7 +2773,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2694,7 +2789,9 @@
       <c r="E48" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F48" s="1"/>
+      <c r="F48" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="G48" s="6">
         <v>1902</v>
       </c>
@@ -2705,7 +2802,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -2719,7 +2816,9 @@
         <v>149</v>
       </c>
       <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>339</v>
+      </c>
       <c r="G49" s="6">
         <v>1942</v>
       </c>
@@ -2728,7 +2827,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2742,7 +2841,9 @@
         <v>151</v>
       </c>
       <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
+      <c r="F50" s="1" t="s">
+        <v>340</v>
+      </c>
       <c r="G50" s="6">
         <v>1954</v>
       </c>
@@ -2751,7 +2852,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -2766,7 +2867,7 @@
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="5"/>
@@ -2776,7 +2877,7 @@
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2791,7 +2892,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="2"/>
@@ -2801,7 +2902,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2816,7 +2917,7 @@
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="1"/>
@@ -2826,7 +2927,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -2841,7 +2942,7 @@
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="1"/>
@@ -2851,7 +2952,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2876,7 +2977,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2901,7 +3002,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2924,7 +3025,7 @@
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2951,7 +3052,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2976,7 +3077,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2995,7 +3096,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -3020,7 +3121,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -3043,7 +3144,7 @@
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -3064,7 +3165,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -3085,7 +3186,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -3110,7 +3211,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -3137,7 +3238,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -3162,7 +3263,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3187,7 +3288,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3210,7 +3311,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3231,7 +3332,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3256,7 +3357,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3281,7 +3382,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -3306,7 +3407,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -3331,7 +3432,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -3352,7 +3453,7 @@
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -3366,7 +3467,9 @@
       <c r="E76" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F76" s="1"/>
+      <c r="F76" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="G76" s="6"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
@@ -3375,12 +3478,12 @@
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1" t="s">
@@ -3389,7 +3492,9 @@
       <c r="E77" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F77" s="1"/>
+      <c r="F77" s="1" t="s">
+        <v>342</v>
+      </c>
       <c r="G77" s="6"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
@@ -3398,7 +3503,7 @@
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -3414,7 +3519,9 @@
       <c r="E78" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F78" s="1"/>
+      <c r="F78" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="G78" s="6" t="s">
         <v>230</v>
       </c>
@@ -3425,7 +3532,7 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -3439,14 +3546,16 @@
         <v>234</v>
       </c>
       <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
+      <c r="F79" s="1" t="s">
+        <v>358</v>
+      </c>
       <c r="G79" s="6"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -3471,7 +3580,7 @@
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3485,7 +3594,9 @@
       <c r="E81" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F81" s="2"/>
+      <c r="F81" s="2" t="s">
+        <v>347</v>
+      </c>
       <c r="G81" s="3"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
@@ -3494,7 +3605,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -3521,7 +3632,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -3542,7 +3653,7 @@
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -3563,7 +3674,7 @@
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -3584,7 +3695,7 @@
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -3611,7 +3722,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -3638,7 +3749,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -3652,14 +3763,16 @@
         <v>258</v>
       </c>
       <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
+      <c r="F88" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="G88" s="6"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -3675,7 +3788,9 @@
       <c r="E89" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F89" s="1"/>
+      <c r="F89" s="1" t="s">
+        <v>350</v>
+      </c>
       <c r="G89" s="6">
         <v>1909</v>
       </c>
@@ -3688,7 +3803,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -3704,7 +3819,9 @@
       <c r="E90" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F90" s="1"/>
+      <c r="F90" s="1" t="s">
+        <v>352</v>
+      </c>
       <c r="G90" s="6">
         <v>1944</v>
       </c>
@@ -3715,7 +3832,7 @@
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -3729,7 +3846,9 @@
         <v>269</v>
       </c>
       <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
+      <c r="F91" s="1" t="s">
+        <v>349</v>
+      </c>
       <c r="G91" s="6">
         <v>1933</v>
       </c>
@@ -3738,7 +3857,7 @@
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -3752,14 +3871,16 @@
         <v>271</v>
       </c>
       <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
+      <c r="F92" s="1" t="s">
+        <v>353</v>
+      </c>
       <c r="G92" s="6"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -3773,7 +3894,9 @@
         <v>272</v>
       </c>
       <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
+      <c r="F93" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="G93" s="6"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1" t="s">
@@ -3782,7 +3905,7 @@
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -3796,7 +3919,9 @@
         <v>275</v>
       </c>
       <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
+      <c r="F94" s="1" t="s">
+        <v>356</v>
+      </c>
       <c r="G94" s="6"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -3805,7 +3930,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -3819,7 +3944,9 @@
         <v>278</v>
       </c>
       <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
+      <c r="F95" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="G95" s="6"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -3828,7 +3955,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -3842,7 +3969,9 @@
         <v>283</v>
       </c>
       <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
+      <c r="F96" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="G96" s="6">
         <v>1931</v>
       </c>
@@ -3853,7 +3982,7 @@
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -3867,7 +3996,9 @@
         <v>285</v>
       </c>
       <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
+      <c r="F97" s="1" t="s">
+        <v>345</v>
+      </c>
       <c r="G97" s="6">
         <v>1954</v>
       </c>
@@ -3876,7 +4007,7 @@
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -3903,7 +4034,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -3917,7 +4048,9 @@
         <v>291</v>
       </c>
       <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
+      <c r="F99" s="1" t="s">
+        <v>343</v>
+      </c>
       <c r="G99" s="6" t="s">
         <v>292</v>
       </c>
@@ -3926,7 +4059,7 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -3940,7 +4073,9 @@
         <v>294</v>
       </c>
       <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
+      <c r="F100" s="1" t="s">
+        <v>344</v>
+      </c>
       <c r="G100" s="6">
         <v>1938</v>
       </c>
@@ -3949,7 +4084,7 @@
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -3966,7 +4101,7 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -3981,7 +4116,7 @@
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0237529D-9C12-44A9-A4C2-6F528D3A3FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519E4333-AE0E-46B9-A654-31D1122E7BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="360">
   <si>
     <t>Ejer</t>
   </si>
@@ -929,9 +929,6 @@
     <t>56.148938, 10.126916</t>
   </si>
   <si>
-    <t>56.148125, 10.126643</t>
-  </si>
-  <si>
     <t>56.148896, 10.125157</t>
   </si>
   <si>
@@ -1004,9 +1001,6 @@
     <t>56.152276, 10.095577</t>
   </si>
   <si>
-    <t>56.158792, 10.119503</t>
-  </si>
-  <si>
     <t>56.157651, 10.117335</t>
   </si>
   <si>
@@ -1113,6 +1107,15 @@
   </si>
   <si>
     <t>56.153553, 10.118423</t>
+  </si>
+  <si>
+    <t>56.149682, 10.125285</t>
+  </si>
+  <si>
+    <t>56.158504, 10.119352</t>
+  </si>
+  <si>
+    <t>56.161302, 10.109074</t>
   </si>
 </sst>
 </file>
@@ -1611,7 +1614,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>8</v>
@@ -1678,7 +1681,7 @@
         <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="1"/>
@@ -1757,7 +1760,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
@@ -1782,7 +1785,7 @@
         <v>38</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>37</v>
@@ -1809,7 +1812,7 @@
         <v>41</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G10" s="6">
         <v>1933</v>
@@ -1919,7 +1922,7 @@
         <v>56</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="1"/>
@@ -1946,7 +1949,7 @@
         <v>57</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="1"/>
@@ -1971,7 +1974,7 @@
         <v>61</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="1"/>
@@ -1996,7 +1999,7 @@
         <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="1"/>
@@ -2021,7 +2024,7 @@
         <v>38</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="5"/>
@@ -2046,7 +2049,7 @@
         <v>38</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="1"/>
@@ -2071,7 +2074,7 @@
         <v>38</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="1"/>
@@ -2096,7 +2099,7 @@
         <v>38</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="1"/>
@@ -2119,7 +2122,7 @@
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G22" s="6">
         <v>1921</v>
@@ -2148,7 +2151,7 @@
         <v>78</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="1"/>
@@ -2172,7 +2175,7 @@
         <v>38</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="1"/>
@@ -2201,7 +2204,7 @@
         <v>86</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="1"/>
@@ -2226,7 +2229,7 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="2"/>
@@ -2249,7 +2252,7 @@
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="5"/>
@@ -2274,7 +2277,7 @@
         <v>91</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G28" s="6">
         <v>1914</v>
@@ -2301,7 +2304,7 @@
         <v>96</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="1"/>
@@ -2326,7 +2329,7 @@
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G30" s="6">
         <v>1936</v>
@@ -2355,7 +2358,7 @@
         <v>38</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G31" s="6">
         <v>1957</v>
@@ -2382,7 +2385,7 @@
         <v>38</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="1"/>
@@ -2407,7 +2410,7 @@
         <v>107</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="1"/>
@@ -2436,7 +2439,7 @@
         <v>112</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="1"/>
@@ -2461,7 +2464,7 @@
         <v>115</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="G35" s="6">
         <v>1870</v>
@@ -2486,7 +2489,7 @@
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="2"/>
@@ -2509,7 +2512,7 @@
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="1"/>
@@ -2536,7 +2539,7 @@
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G38" s="6">
         <v>1942</v>
@@ -2561,7 +2564,7 @@
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G39" s="6">
         <v>1928</v>
@@ -2586,7 +2589,7 @@
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="1"/>
@@ -2613,7 +2616,7 @@
         <v>132</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G41" s="6">
         <v>1932</v>
@@ -2642,7 +2645,7 @@
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="1"/>
@@ -2667,7 +2670,7 @@
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G43" s="6">
         <v>1937</v>
@@ -2694,7 +2697,7 @@
         <v>132</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G44" s="6">
         <v>1943</v>
@@ -2719,7 +2722,7 @@
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G45" s="6">
         <v>1897</v>
@@ -2741,7 +2744,9 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
+      <c r="F46" s="2" t="s">
+        <v>359</v>
+      </c>
       <c r="G46" s="3"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -2763,7 +2768,7 @@
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="1"/>
@@ -2790,7 +2795,7 @@
         <v>147</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G48" s="6">
         <v>1902</v>
@@ -2817,7 +2822,7 @@
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G49" s="6">
         <v>1942</v>
@@ -2842,7 +2847,7 @@
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G50" s="6">
         <v>1954</v>
@@ -2867,7 +2872,7 @@
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="5"/>
@@ -2892,7 +2897,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="2"/>
@@ -2917,7 +2922,7 @@
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="1"/>
@@ -2942,7 +2947,7 @@
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="1"/>
@@ -3468,7 +3473,7 @@
         <v>132</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G76" s="6"/>
       <c r="H76" s="1"/>
@@ -3493,7 +3498,7 @@
         <v>132</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G77" s="6"/>
       <c r="H77" s="1"/>
@@ -3520,7 +3525,7 @@
         <v>232</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>230</v>
@@ -3547,7 +3552,7 @@
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G79" s="6"/>
       <c r="H79" s="1"/>
@@ -3595,7 +3600,7 @@
         <v>112</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G81" s="3"/>
       <c r="H81" s="2"/>
@@ -3764,7 +3769,7 @@
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G88" s="6"/>
       <c r="H88" s="1"/>
@@ -3789,7 +3794,7 @@
         <v>263</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G89" s="6">
         <v>1909</v>
@@ -3820,7 +3825,7 @@
         <v>266</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G90" s="6">
         <v>1944</v>
@@ -3847,7 +3852,7 @@
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G91" s="6">
         <v>1933</v>
@@ -3872,7 +3877,7 @@
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G92" s="6"/>
       <c r="H92" s="1"/>
@@ -3895,7 +3900,7 @@
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G93" s="6"/>
       <c r="H93" s="1"/>
@@ -3920,7 +3925,7 @@
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G94" s="6"/>
       <c r="H94" s="1"/>
@@ -3945,7 +3950,7 @@
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G95" s="6"/>
       <c r="H95" s="1"/>
@@ -3970,7 +3975,7 @@
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G96" s="6">
         <v>1931</v>
@@ -3997,7 +4002,7 @@
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G97" s="6">
         <v>1954</v>
@@ -4049,7 +4054,7 @@
       </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G99" s="6" t="s">
         <v>292</v>
@@ -4074,7 +4079,7 @@
       </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G100" s="6">
         <v>1938</v>

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erikl\Documents\GitHub\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIS\Github Update\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519E4333-AE0E-46B9-A654-31D1122E7BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8C320F-30A8-4EB2-A352-AEAC9F266CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="361">
   <si>
     <t>Ejer</t>
   </si>
@@ -1116,6 +1116,9 @@
   </si>
   <si>
     <t>56.161302, 10.109074</t>
+  </si>
+  <si>
+    <t>56.183684, 10.130028</t>
   </si>
 </sst>
 </file>
@@ -1548,21 +1551,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9410E6E1-B6FD-499D-B70E-01FA93ABCF11}">
   <dimension ref="A1:K103"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.81640625" customWidth="1"/>
-    <col min="3" max="3" width="26.54296875" customWidth="1"/>
-    <col min="4" max="4" width="28.1796875" customWidth="1"/>
-    <col min="5" max="5" width="17.26953125" customWidth="1"/>
+    <col min="1" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="28.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="21.54296875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="25.1796875" customWidth="1"/>
-    <col min="9" max="9" width="25.7265625" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" customWidth="1"/>
-    <col min="11" max="11" width="36.1796875" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="36.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1597,7 +1600,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1626,7 +1629,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1645,7 +1648,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1664,7 +1667,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1689,7 +1692,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1716,7 +1719,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1747,7 +1750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1768,7 +1771,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1797,7 +1800,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1826,7 +1829,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1853,7 +1856,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1880,7 +1883,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1905,7 +1908,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1932,7 +1935,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1957,7 +1960,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1982,7 +1985,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2007,7 +2010,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -2032,7 +2035,7 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2057,7 +2060,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2082,7 +2085,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2107,7 +2110,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2134,7 +2137,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2158,7 +2161,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2187,7 +2190,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2216,7 +2219,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2237,7 +2240,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -2260,7 +2263,7 @@
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2289,7 +2292,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2314,7 +2317,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2341,7 +2344,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2368,7 +2371,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2393,7 +2396,7 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2422,7 +2425,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2447,7 +2450,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2476,7 +2479,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2497,7 +2500,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2524,7 +2527,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2549,7 +2552,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2574,7 +2577,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2599,7 +2602,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2630,7 +2633,7 @@
         <v>7716</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2655,7 +2658,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2680,7 +2683,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -2707,7 +2710,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -2732,7 +2735,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2753,7 +2756,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2778,7 +2781,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2807,7 +2810,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -2832,7 +2835,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2857,7 +2860,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -2882,7 +2885,7 @@
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2907,7 +2910,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2932,7 +2935,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -2957,7 +2960,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2982,7 +2985,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -3007,7 +3010,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -3030,7 +3033,7 @@
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -3057,7 +3060,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -3082,7 +3085,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3101,7 +3104,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -3126,7 +3129,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -3149,7 +3152,7 @@
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -3170,7 +3173,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -3191,7 +3194,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -3216,7 +3219,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -3243,7 +3246,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -3268,7 +3271,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3293,7 +3296,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3316,7 +3319,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3337,7 +3340,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3362,7 +3365,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3387,7 +3390,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -3412,7 +3415,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -3437,7 +3440,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -3458,7 +3461,7 @@
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -3483,7 +3486,7 @@
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -3508,7 +3511,7 @@
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -3537,7 +3540,7 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -3560,7 +3563,7 @@
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -3585,7 +3588,7 @@
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3610,7 +3613,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -3637,7 +3640,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -3658,7 +3661,7 @@
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -3679,7 +3682,7 @@
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -3693,14 +3696,16 @@
       <c r="E85" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F85" s="1"/>
+      <c r="F85" s="1" t="s">
+        <v>360</v>
+      </c>
       <c r="G85" s="6"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -3727,7 +3732,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -3754,7 +3759,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -3777,7 +3782,7 @@
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -3808,7 +3813,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -3837,7 +3842,7 @@
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -3862,7 +3867,7 @@
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -3885,7 +3890,7 @@
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -3910,7 +3915,7 @@
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -3935,7 +3940,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -3960,7 +3965,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -3987,7 +3992,7 @@
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -4012,7 +4017,7 @@
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -4039,7 +4044,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -4064,7 +4069,7 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -4089,7 +4094,7 @@
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -4106,7 +4111,7 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -4121,7 +4126,7 @@
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>

--- a/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
+++ b/Gartnerier i Brabrand/oversigt_over_gartnerierne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIS\Github Update\Gartnerier-i-Brabrand\Gartnerier i Brabrand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8C320F-30A8-4EB2-A352-AEAC9F266CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C102E76B-BDEB-4401-B0E5-18AFFACC658A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C4A0B6AA-D64C-40C5-A9A2-780F03B91B71}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="386">
   <si>
     <t>Ejer</t>
   </si>
@@ -1119,6 +1119,81 @@
   </si>
   <si>
     <t>56.183684, 10.130028</t>
+  </si>
+  <si>
+    <t>56.148693, 10.127614</t>
+  </si>
+  <si>
+    <t>56.148759, 10.128644</t>
+  </si>
+  <si>
+    <t>56.147922, 10.128461</t>
+  </si>
+  <si>
+    <t>56.149016, 10.143353</t>
+  </si>
+  <si>
+    <t>56.148968, 10.144919</t>
+  </si>
+  <si>
+    <t>56.150928, 10.142827</t>
+  </si>
+  <si>
+    <t>56.146957, 10.145772</t>
+  </si>
+  <si>
+    <t>56.147298, 10.143766</t>
+  </si>
+  <si>
+    <t>56.147372, 10.141277</t>
+  </si>
+  <si>
+    <t>56.147501, 10.140381</t>
+  </si>
+  <si>
+    <t>56.174144, 10.109074</t>
+  </si>
+  <si>
+    <t>56.164653, 10.083250</t>
+  </si>
+  <si>
+    <t>56.181203, 10.125757</t>
+  </si>
+  <si>
+    <t>56.176706, 10.108184</t>
+  </si>
+  <si>
+    <t>56.168751, 10.083969</t>
+  </si>
+  <si>
+    <t>56.157722, 10.083711</t>
+  </si>
+  <si>
+    <t>56.163954, 10.081930</t>
+  </si>
+  <si>
+    <t>56.153319, 10.111102</t>
+  </si>
+  <si>
+    <t>56.153235, 10.112236</t>
+  </si>
+  <si>
+    <t>56.153250, 10.112478</t>
+  </si>
+  <si>
+    <t>56.153325, 10.111724</t>
+  </si>
+  <si>
+    <t>56.153344, 10.111402</t>
+  </si>
+  <si>
+    <t>56.155040, 10.110217</t>
+  </si>
+  <si>
+    <t>56.155571, 10.112947</t>
+  </si>
+  <si>
+    <t>56.174885, 10.090674</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1209,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1150,6 +1225,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1194,7 +1275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1216,6 +1297,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1639,7 +1724,9 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>361</v>
+      </c>
       <c r="G3" s="3">
         <v>1916</v>
       </c>
@@ -1660,7 +1747,9 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>362</v>
+      </c>
       <c r="G4" s="6"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -1706,7 +1795,9 @@
       <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="G6" s="6">
         <v>1937</v>
       </c>
@@ -1843,7 +1934,9 @@
         <v>47</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>366</v>
+      </c>
       <c r="G11" s="8">
         <v>1909</v>
       </c>
@@ -1870,7 +1963,9 @@
         <v>47</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>364</v>
+      </c>
       <c r="G12" s="8">
         <v>1909</v>
       </c>
@@ -1899,7 +1994,9 @@
       <c r="E13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>365</v>
+      </c>
       <c r="G13" s="8"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5" t="s">
@@ -2961,52 +3058,56 @@
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="A55" s="11">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1" t="s">
+      <c r="E55" s="11"/>
+      <c r="F55" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="G55" s="12"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1" t="s">
+      <c r="J55" s="11"/>
+      <c r="K55" s="11" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="A56" s="11">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1" t="s">
+      <c r="E56" s="11"/>
+      <c r="F56" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="G56" s="12"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1" t="s">
+      <c r="J56" s="11"/>
+      <c r="K56" s="11" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3024,7 +3125,9 @@
         <v>173</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
+      <c r="F57" s="1" t="s">
+        <v>383</v>
+      </c>
       <c r="G57" s="6">
         <v>1956</v>
       </c>
@@ -3047,7 +3150,9 @@
         <v>176</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
+      <c r="F58" s="1" t="s">
+        <v>384</v>
+      </c>
       <c r="G58" s="6">
         <v>1926</v>
       </c>
@@ -3074,7 +3179,9 @@
         <v>176</v>
       </c>
       <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>384</v>
+      </c>
       <c r="G59" s="6"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
@@ -3105,27 +3212,29 @@
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="A61" s="11">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1" t="s">
+      <c r="E61" s="11"/>
+      <c r="F61" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="G61" s="12"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1" t="s">
+      <c r="J61" s="11"/>
+      <c r="K61" s="11" t="s">
         <v>182</v>
       </c>
     </row>
@@ -3143,7 +3252,9 @@
         <v>185</v>
       </c>
       <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
+      <c r="F62" s="1" t="s">
+        <v>380</v>
+      </c>
       <c r="G62" s="6">
         <v>1948</v>
       </c>
@@ -3166,7 +3277,9 @@
         <v>186</v>
       </c>
       <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
+      <c r="F63" s="1" t="s">
+        <v>381</v>
+      </c>
       <c r="G63" s="6"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -3187,7 +3300,9 @@
         <v>186</v>
       </c>
       <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
+      <c r="F64" s="1" t="s">
+        <v>382</v>
+      </c>
       <c r="G64" s="6"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -3208,7 +3323,9 @@
         <v>185</v>
       </c>
       <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
+      <c r="F65" s="1" t="s">
+        <v>379</v>
+      </c>
       <c r="G65" s="6">
         <v>1961</v>
       </c>
@@ -3233,7 +3350,9 @@
         <v>196</v>
       </c>
       <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>378</v>
+      </c>
       <c r="G66" s="6">
         <v>1932</v>
       </c>
@@ -3247,54 +3366,58 @@
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+      <c r="A67" s="11">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1" t="s">
+      <c r="E67" s="11"/>
+      <c r="F67" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="G67" s="12"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1" t="s">
+      <c r="J67" s="11"/>
+      <c r="K67" s="11" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+      <c r="A68" s="11">
         <v>67</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="6">
+      <c r="E68" s="11"/>
+      <c r="F68" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="G68" s="12">
         <v>1939</v>
       </c>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1" t="s">
+      <c r="H68" s="11"/>
+      <c r="I68" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
@@ -3308,7 +3431,9 @@
         <v>203</v>
       </c>
       <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
+      <c r="F69" s="2" t="s">
+        <v>377</v>
+      </c>
       <c r="G69" s="3"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
@@ -3331,7 +3456,9 @@
         <v>205</v>
       </c>
       <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
+      <c r="F70" s="2" t="s">
+        <v>376</v>
+      </c>
       <c r="G70" s="3"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -3577,7 +3704,9 @@
         <v>237</v>
       </c>
       <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
+      <c r="F80" s="1" t="s">
+        <v>367</v>
+      </c>
       <c r="G80" s="6">
         <v>1899</v>
       </c>
@@ -3627,7 +3756,9 @@
         <v>243</v>
       </c>
       <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
+      <c r="F82" s="1" t="s">
+        <v>368</v>
+      </c>
       <c r="G82" s="6">
         <v>1899</v>
       </c>
@@ -3654,7 +3785,9 @@
         <v>244</v>
       </c>
       <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
+      <c r="F83" s="1" t="s">
+        <v>369</v>
+      </c>
       <c r="G83" s="6"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -3675,7 +3808,9 @@
         <v>200</v>
       </c>
       <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
+      <c r="F84" s="1" t="s">
+        <v>370</v>
+      </c>
       <c r="G84" s="6"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -3683,52 +3818,54 @@
       <c r="K84" s="1"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+      <c r="A85" s="11">
         <v>84</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1" t="s">
+      <c r="D85" s="11"/>
+      <c r="E85" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="G85" s="6"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
-      <c r="K85" s="1"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+      <c r="A86" s="11">
         <v>85</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="6">
+      <c r="E86" s="11"/>
+      <c r="F86" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="G86" s="12">
         <v>1944</v>
       </c>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1" t="s">
+      <c r="H86" s="11"/>
+      <c r="I86" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1" t="s">
+      <c r="J86" s="11"/>
+      <c r="K86" s="11" t="s">
         <v>252</v>
       </c>
     </row>
